--- a/04_DESIGN_TABLES/DesignTable_6803.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6803.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V39"/>
+  <dimension ref="A1:W40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -583,6 +583,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -654,12 +659,17 @@
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p059-t02: agrees on LEG1@DRIVE, LEG2@DRIVE, LEG3@DRIVE, HEXB@HEX, Y@REF, D1@BORE, D2@BORE, D3@BORE</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>6803-04-04-04-NWO-FG</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1138,17 @@
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p059-t02: agrees on LEG1@DRIVE, LEG2@DRIVE, LEG3@DRIVE, HEXB@HEX, Y@REF, D1@BORE, D2@BORE, D3@BORE</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>6803-06-06-06-NWO-FG</t>
         </is>
       </c>
     </row>
@@ -3387,6 +3402,95 @@
       <c r="V39" t="inlineStr">
         <is>
           <t>6803-24-24-24-NWO-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>6803-04-04-06-NWO-FG</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>6803-04-04-06-NWO-FG</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>7/16-20 x 7/16-20 x 9/16-18</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): legs / locknut hex / flats / bores from the Brennan TFA catalog p.59; JIC ends MS33656J; ORB branch end data from the table's own -06 ORB rows (A5) = the ORB library</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.59 alone; marked DimSource BRENNAN</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>6803-04-04-06-NWO-FG</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
